--- a/E8 Singapore.xlsx
+++ b/E8 Singapore.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="258">
   <si>
     <t>tissueID</t>
   </si>
@@ -245,6 +245,9 @@
     <t>basisOfRecord</t>
   </si>
   <si>
+    <t>sampleEnteredBy</t>
+  </si>
+  <si>
     <t>expedition</t>
   </si>
   <si>
@@ -464,7 +467,7 @@
     <t>Medina Lab</t>
   </si>
   <si>
-    <t xml:space="preserve"> Penn State</t>
+    <t>PSU</t>
   </si>
   <si>
     <t>Mucus</t>
@@ -611,13 +614,10 @@
     <t>E3</t>
   </si>
   <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>disease</t>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>TRUE</t>
   </si>
   <si>
     <t>turf</t>
@@ -656,15 +656,6 @@
     <t>bristled_white_sea_whip</t>
   </si>
   <si>
-    <t>2_corals</t>
-  </si>
-  <si>
-    <t>fungia</t>
-  </si>
-  <si>
-    <t>3_corals</t>
-  </si>
-  <si>
     <t>10.1371/journal.pone.0003222 | 10.1098/rstb.2014.0010|10.1038/sdata.2016.17</t>
   </si>
   <si>
@@ -789,6 +780,9 @@
   </si>
   <si>
     <t>PreservedSpecimen</t>
+  </si>
+  <si>
+    <t>Colin Howe|Vivian Li|Eric Crandall</t>
   </si>
   <si>
     <t>E8</t>
@@ -1075,25 +1069,28 @@
       <c r="CA1" t="s">
         <v>77</v>
       </c>
+      <c r="CB1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
         <v>1.160517</v>
@@ -1102,7 +1099,7 @@
         <v>103.740444</v>
       </c>
       <c r="I2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J2" t="n">
         <v>3.048</v>
@@ -1114,24 +1111,24 @@
       <c r="M2"/>
       <c r="N2"/>
       <c r="O2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W2"/>
       <c r="X2" t="n">
@@ -1144,7 +1141,7 @@
         <v>21.0</v>
       </c>
       <c r="AA2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB2"/>
       <c r="AC2"/>
@@ -1158,14 +1155,14 @@
       <c r="AI2"/>
       <c r="AJ2"/>
       <c r="AK2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL2" t="n">
         <v>1.0</v>
       </c>
       <c r="AM2"/>
       <c r="AN2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO2" t="n">
         <v>1.0</v>
@@ -1177,83 +1174,83 @@
       <c r="AR2"/>
       <c r="AS2"/>
       <c r="AT2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU2" t="n">
         <v>0.0</v>
       </c>
       <c r="AV2"/>
       <c r="AW2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY2"/>
       <c r="AZ2"/>
       <c r="BA2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB2"/>
       <c r="BC2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="BE2" t="n">
         <v>46731.0</v>
       </c>
       <c r="BF2" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI2" t="s">
         <v>228</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>229</v>
       </c>
-      <c r="BH2" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>232</v>
-      </c>
       <c r="BK2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="BL2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BM2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BN2" t="n">
         <v>1.282358148E8</v>
       </c>
       <c r="BO2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ2" t="n">
         <v>4.5</v>
       </c>
       <c r="BR2" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU2" t="s">
         <v>253</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BV2" t="s">
         <v>254</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>257</v>
       </c>
       <c r="BW2" t="n">
         <v>2015.0</v>
@@ -1265,30 +1262,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA2" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
         <v>1.160517</v>
@@ -1297,7 +1297,7 @@
         <v>103.740444</v>
       </c>
       <c r="I3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J3" t="n">
         <v>2.4383999999999997</v>
@@ -1309,24 +1309,24 @@
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R3"/>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W3"/>
       <c r="X3" t="n">
@@ -1339,16 +1339,16 @@
         <v>29.0</v>
       </c>
       <c r="AA3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AB3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC3"/>
       <c r="AD3"/>
       <c r="AE3"/>
       <c r="AF3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG3" t="n">
         <v>0.0</v>
@@ -1357,12 +1357,12 @@
       <c r="AI3"/>
       <c r="AJ3"/>
       <c r="AK3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL3"/>
       <c r="AM3"/>
       <c r="AN3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO3" t="n">
         <v>1.0</v>
@@ -1374,83 +1374,83 @@
       <c r="AR3"/>
       <c r="AS3"/>
       <c r="AT3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU3" t="n">
         <v>0.0</v>
       </c>
       <c r="AV3"/>
       <c r="AW3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY3"/>
       <c r="AZ3"/>
       <c r="BA3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB3"/>
       <c r="BC3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="BE3" t="n">
         <v>46731.0</v>
       </c>
       <c r="BF3" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI3" t="s">
         <v>228</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BJ3" t="s">
         <v>229</v>
       </c>
-      <c r="BH3" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>232</v>
-      </c>
       <c r="BK3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="BL3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BM3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BN3" t="n">
         <v>1.282358148E8</v>
       </c>
       <c r="BO3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ3" t="n">
         <v>4.5</v>
       </c>
       <c r="BR3" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU3" t="s">
         <v>253</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BV3" t="s">
         <v>254</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>257</v>
       </c>
       <c r="BW3" t="n">
         <v>2015.0</v>
@@ -1462,30 +1462,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA3" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
         <v>1.160517</v>
@@ -1494,7 +1497,7 @@
         <v>103.740444</v>
       </c>
       <c r="I4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J4" t="n">
         <v>6.096</v>
@@ -1506,24 +1509,24 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="V4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W4"/>
       <c r="X4" t="n">
@@ -1536,18 +1539,18 @@
         <v>8.0</v>
       </c>
       <c r="AA4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB4"/>
       <c r="AC4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD4" t="n">
         <v>0.0</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG4" t="n">
         <v>0.0</v>
@@ -1556,14 +1559,14 @@
       <c r="AI4"/>
       <c r="AJ4"/>
       <c r="AK4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL4" t="n">
         <v>2.0</v>
       </c>
       <c r="AM4"/>
       <c r="AN4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO4" t="n">
         <v>1.0</v>
@@ -1575,81 +1578,81 @@
       <c r="AR4"/>
       <c r="AS4"/>
       <c r="AT4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU4" t="n">
         <v>0.0</v>
       </c>
       <c r="AV4"/>
       <c r="AW4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY4"/>
       <c r="AZ4"/>
       <c r="BA4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BB4"/>
       <c r="BC4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="BE4" t="n">
         <v>486217.0</v>
       </c>
       <c r="BF4" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI4" t="s">
         <v>228</v>
       </c>
-      <c r="BG4" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH4" t="s">
+      <c r="BJ4" t="s">
         <v>230</v>
       </c>
-      <c r="BI4" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>233</v>
-      </c>
       <c r="BK4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="BL4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BM4"/>
       <c r="BN4" t="n">
         <v>7.53556275E7</v>
       </c>
       <c r="BO4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ4" t="n">
         <v>4.5</v>
       </c>
       <c r="BR4" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU4" t="s">
         <v>253</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BV4" t="s">
         <v>254</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>257</v>
       </c>
       <c r="BW4" t="n">
         <v>2015.0</v>
@@ -1661,30 +1664,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA4" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
         <v>1.160517</v>
@@ -1693,7 +1699,7 @@
         <v>103.740444</v>
       </c>
       <c r="I5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J5" t="n">
         <v>6.096</v>
@@ -1705,24 +1711,24 @@
       <c r="M5"/>
       <c r="N5"/>
       <c r="O5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R5"/>
       <c r="S5"/>
       <c r="T5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="V5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W5"/>
       <c r="X5" t="n">
@@ -1735,38 +1741,38 @@
         <v>20.0</v>
       </c>
       <c r="AA5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB5"/>
       <c r="AC5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD5" t="n">
         <v>0.0</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG5" t="n">
         <v>0.0</v>
       </c>
       <c r="AH5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI5" t="n">
         <v>10.0</v>
       </c>
       <c r="AJ5"/>
       <c r="AK5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL5" t="n">
         <v>80.0</v>
       </c>
       <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO5" t="n">
         <v>1.0</v>
@@ -1778,81 +1784,81 @@
       <c r="AR5"/>
       <c r="AS5"/>
       <c r="AT5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU5" t="n">
         <v>0.0</v>
       </c>
       <c r="AV5"/>
       <c r="AW5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY5"/>
       <c r="AZ5"/>
       <c r="BA5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB5"/>
       <c r="BC5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="BE5" t="n">
         <v>486217.0</v>
       </c>
       <c r="BF5" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI5" t="s">
         <v>228</v>
       </c>
-      <c r="BG5" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH5" t="s">
+      <c r="BJ5" t="s">
         <v>230</v>
       </c>
-      <c r="BI5" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>233</v>
-      </c>
       <c r="BK5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="BL5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BM5"/>
       <c r="BN5" t="n">
         <v>7.53556275E7</v>
       </c>
       <c r="BO5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ5" t="n">
         <v>4.5</v>
       </c>
       <c r="BR5" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU5" t="s">
         <v>253</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="BV5" t="s">
         <v>254</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>257</v>
       </c>
       <c r="BW5" t="n">
         <v>2015.0</v>
@@ -1864,30 +1870,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA5" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G6" t="n">
         <v>1.160517</v>
@@ -1896,7 +1905,7 @@
         <v>103.740444</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J6" t="n">
         <v>5.486400000000001</v>
@@ -1908,42 +1917,42 @@
       <c r="M6"/>
       <c r="N6"/>
       <c r="O6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R6"/>
       <c r="S6"/>
       <c r="T6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="W6"/>
       <c r="X6"/>
       <c r="Y6"/>
       <c r="Z6"/>
       <c r="AA6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AB6"/>
       <c r="AC6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD6" t="n">
         <v>0.0</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG6" t="n">
         <v>0.0</v>
@@ -1955,7 +1964,7 @@
       <c r="AL6"/>
       <c r="AM6"/>
       <c r="AN6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO6" t="n">
         <v>0.0</v>
@@ -1970,74 +1979,74 @@
       <c r="AU6"/>
       <c r="AV6"/>
       <c r="AW6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY6"/>
       <c r="AZ6"/>
       <c r="BA6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB6"/>
       <c r="BC6" t="s">
+        <v>214</v>
+      </c>
+      <c r="BD6" t="s">
         <v>217</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>220</v>
       </c>
       <c r="BE6" t="n">
         <v>244861.0</v>
       </c>
       <c r="BF6" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI6" t="s">
         <v>228</v>
       </c>
-      <c r="BG6" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI6" t="s">
+      <c r="BJ6" t="s">
         <v>231</v>
       </c>
-      <c r="BJ6" t="s">
-        <v>234</v>
-      </c>
       <c r="BK6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="BL6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BM6"/>
       <c r="BN6" t="n">
         <v>8.016306614999999E7</v>
       </c>
       <c r="BO6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.5</v>
       </c>
       <c r="BR6" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU6" t="s">
         <v>253</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BV6" t="s">
         <v>254</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>257</v>
       </c>
       <c r="BW6" t="n">
         <v>2015.0</v>
@@ -2049,30 +2058,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA6" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G7" t="n">
         <v>1.160517</v>
@@ -2081,7 +2093,7 @@
         <v>103.740444</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J7" t="n">
         <v>4.2672</v>
@@ -2093,24 +2105,24 @@
       <c r="M7"/>
       <c r="N7"/>
       <c r="O7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R7"/>
       <c r="S7"/>
       <c r="T7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="V7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="W7"/>
       <c r="X7" t="n">
@@ -2123,38 +2135,38 @@
         <v>50.0</v>
       </c>
       <c r="AA7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB7"/>
       <c r="AC7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD7" t="n">
         <v>0.0</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG7" t="n">
         <v>0.0</v>
       </c>
       <c r="AH7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI7" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ7"/>
       <c r="AK7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL7" t="n">
         <v>0.0</v>
       </c>
       <c r="AM7"/>
       <c r="AN7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO7" t="n">
         <v>0.0</v>
@@ -2166,83 +2178,83 @@
       </c>
       <c r="AS7"/>
       <c r="AT7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU7" t="n">
         <v>0.0</v>
       </c>
       <c r="AV7"/>
       <c r="AW7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY7"/>
       <c r="AZ7" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="BA7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB7"/>
       <c r="BC7" t="s">
+        <v>214</v>
+      </c>
+      <c r="BD7" t="s">
         <v>217</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>220</v>
       </c>
       <c r="BE7" t="n">
         <v>244861.0</v>
       </c>
       <c r="BF7" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI7" t="s">
         <v>228</v>
       </c>
-      <c r="BG7" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI7" t="s">
+      <c r="BJ7" t="s">
         <v>231</v>
       </c>
-      <c r="BJ7" t="s">
-        <v>234</v>
-      </c>
       <c r="BK7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="BL7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BM7"/>
       <c r="BN7" t="n">
         <v>8.016306614999999E7</v>
       </c>
       <c r="BO7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.5</v>
       </c>
       <c r="BR7" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU7" t="s">
         <v>253</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BV7" t="s">
         <v>254</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>257</v>
       </c>
       <c r="BW7" t="n">
         <v>2015.0</v>
@@ -2254,30 +2266,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA7" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
         <v>1.160517</v>
@@ -2286,7 +2301,7 @@
         <v>103.740444</v>
       </c>
       <c r="I8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J8" t="n">
         <v>3.6576</v>
@@ -2298,24 +2313,24 @@
       <c r="M8"/>
       <c r="N8"/>
       <c r="O8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R8"/>
       <c r="S8"/>
       <c r="T8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="W8"/>
       <c r="X8" t="n">
@@ -2328,7 +2343,7 @@
         <v>100.0</v>
       </c>
       <c r="AA8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB8"/>
       <c r="AC8"/>
@@ -2337,27 +2352,27 @@
       </c>
       <c r="AE8"/>
       <c r="AF8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG8" t="n">
         <v>0.0</v>
       </c>
       <c r="AH8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI8" t="n">
         <v>10.0</v>
       </c>
       <c r="AJ8"/>
       <c r="AK8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL8" t="n">
         <v>15.0</v>
       </c>
       <c r="AM8"/>
       <c r="AN8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO8" t="n">
         <v>1.0</v>
@@ -2369,81 +2384,81 @@
       <c r="AR8"/>
       <c r="AS8"/>
       <c r="AT8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU8" t="n">
         <v>0.0</v>
       </c>
       <c r="AV8"/>
       <c r="AW8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY8"/>
       <c r="AZ8"/>
       <c r="BA8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB8"/>
       <c r="BC8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="BE8" t="n">
         <v>570133.0</v>
       </c>
       <c r="BF8" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI8" t="s">
         <v>228</v>
       </c>
-      <c r="BG8" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="BL8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="BM8"/>
       <c r="BN8" t="n">
         <v>9.504899898E7</v>
       </c>
       <c r="BO8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.5</v>
       </c>
       <c r="BR8" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU8" t="s">
         <v>253</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BV8" t="s">
         <v>254</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>257</v>
       </c>
       <c r="BW8" t="n">
         <v>2015.0</v>
@@ -2455,30 +2470,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA8" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" t="n">
         <v>1.160517</v>
@@ -2487,7 +2505,7 @@
         <v>103.740444</v>
       </c>
       <c r="I9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J9" t="n">
         <v>5.486400000000001</v>
@@ -2499,24 +2517,24 @@
       <c r="M9"/>
       <c r="N9"/>
       <c r="O9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R9"/>
       <c r="S9"/>
       <c r="T9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="W9"/>
       <c r="X9" t="n">
@@ -2529,7 +2547,7 @@
         <v>9.0</v>
       </c>
       <c r="AA9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
@@ -2538,27 +2556,27 @@
       </c>
       <c r="AE9"/>
       <c r="AF9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG9" t="n">
         <v>0.0</v>
       </c>
       <c r="AH9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI9" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ9"/>
       <c r="AK9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL9" t="n">
         <v>30.0</v>
       </c>
       <c r="AM9"/>
       <c r="AN9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO9" t="n">
         <v>3.0</v>
@@ -2574,81 +2592,81 @@
         <v>207</v>
       </c>
       <c r="AT9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU9" t="n">
         <v>0.0</v>
       </c>
       <c r="AV9"/>
       <c r="AW9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY9"/>
       <c r="AZ9"/>
       <c r="BA9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB9"/>
       <c r="BC9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="BE9" t="n">
         <v>570133.0</v>
       </c>
       <c r="BF9" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI9" t="s">
         <v>228</v>
       </c>
-      <c r="BG9" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="BL9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="BM9"/>
       <c r="BN9" t="n">
         <v>9.504899898E7</v>
       </c>
       <c r="BO9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.5</v>
       </c>
       <c r="BR9" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU9" t="s">
         <v>253</v>
       </c>
-      <c r="BS9" t="s">
+      <c r="BV9" t="s">
         <v>254</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>257</v>
       </c>
       <c r="BW9" t="n">
         <v>2015.0</v>
@@ -2660,30 +2678,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA9" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G10" t="n">
         <v>1.160517</v>
@@ -2692,7 +2713,7 @@
         <v>103.740444</v>
       </c>
       <c r="I10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J10" t="n">
         <v>3.048</v>
@@ -2704,24 +2725,24 @@
       <c r="M10"/>
       <c r="N10"/>
       <c r="O10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R10"/>
       <c r="S10"/>
       <c r="T10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="W10"/>
       <c r="X10" t="n">
@@ -2734,38 +2755,38 @@
         <v>100.0</v>
       </c>
       <c r="AA10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB10"/>
       <c r="AC10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD10" t="n">
         <v>3.0</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG10" t="n">
         <v>0.0</v>
       </c>
       <c r="AH10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI10" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ10"/>
       <c r="AK10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL10" t="n">
         <v>12.0</v>
       </c>
       <c r="AM10"/>
       <c r="AN10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO10"/>
       <c r="AP10"/>
@@ -2775,85 +2796,85 @@
       </c>
       <c r="AS10"/>
       <c r="AT10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU10" t="n">
         <v>0.0</v>
       </c>
       <c r="AV10"/>
       <c r="AW10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY10" t="s">
         <v>211</v>
       </c>
       <c r="AZ10"/>
       <c r="BA10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB10"/>
       <c r="BC10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="BE10" t="n">
         <v>46694.0</v>
       </c>
       <c r="BF10" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI10" t="s">
         <v>228</v>
       </c>
-      <c r="BG10" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="BL10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BM10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BN10" t="n">
         <v>9.69464839E7</v>
       </c>
       <c r="BO10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.5</v>
       </c>
       <c r="BR10" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU10" t="s">
         <v>253</v>
       </c>
-      <c r="BS10" t="s">
+      <c r="BV10" t="s">
         <v>254</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>257</v>
       </c>
       <c r="BW10" t="n">
         <v>2015.0</v>
@@ -2865,30 +2886,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA10" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" t="n">
         <v>1.160517</v>
@@ -2897,7 +2921,7 @@
         <v>103.740444</v>
       </c>
       <c r="I11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J11" t="n">
         <v>4.572</v>
@@ -2909,24 +2933,24 @@
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R11"/>
       <c r="S11"/>
       <c r="T11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="V11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="W11"/>
       <c r="X11" t="n">
@@ -2939,11 +2963,11 @@
         <v>20.0</v>
       </c>
       <c r="AA11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB11"/>
       <c r="AC11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD11" t="n">
         <v>15.0</v>
@@ -2954,21 +2978,21 @@
         <v>0.0</v>
       </c>
       <c r="AH11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI11" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ11"/>
       <c r="AK11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL11" t="n">
         <v>0.0</v>
       </c>
       <c r="AM11"/>
       <c r="AN11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO11" t="n">
         <v>0.0</v>
@@ -2980,83 +3004,83 @@
       </c>
       <c r="AS11"/>
       <c r="AT11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU11" t="n">
         <v>0.0</v>
       </c>
       <c r="AV11"/>
       <c r="AW11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY11"/>
       <c r="AZ11"/>
       <c r="BA11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB11"/>
       <c r="BC11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="BE11" t="n">
         <v>46694.0</v>
       </c>
       <c r="BF11" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI11" t="s">
         <v>228</v>
       </c>
-      <c r="BG11" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="BL11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BM11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BN11" t="n">
         <v>9.69464839E7</v>
       </c>
       <c r="BO11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.5</v>
       </c>
       <c r="BR11" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU11" t="s">
         <v>253</v>
       </c>
-      <c r="BS11" t="s">
+      <c r="BV11" t="s">
         <v>254</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>257</v>
       </c>
       <c r="BW11" t="n">
         <v>2015.0</v>
@@ -3068,30 +3092,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA11" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G12" t="n">
         <v>1.160517</v>
@@ -3100,7 +3127,7 @@
         <v>103.740444</v>
       </c>
       <c r="I12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
@@ -3112,24 +3139,24 @@
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R12"/>
       <c r="S12"/>
       <c r="T12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W12"/>
       <c r="X12" t="n">
@@ -3142,38 +3169,38 @@
         <v>30.0</v>
       </c>
       <c r="AA12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB12"/>
       <c r="AC12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD12" t="n">
         <v>5.0</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG12" t="n">
         <v>0.0</v>
       </c>
       <c r="AH12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI12" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ12"/>
       <c r="AK12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL12" t="n">
         <v>10.0</v>
       </c>
       <c r="AM12"/>
       <c r="AN12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO12" t="n">
         <v>1.0</v>
@@ -3187,81 +3214,81 @@
       </c>
       <c r="AS12"/>
       <c r="AT12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AU12" t="n">
         <v>5.0</v>
       </c>
       <c r="AV12"/>
       <c r="AW12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY12"/>
       <c r="AZ12"/>
       <c r="BA12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB12"/>
       <c r="BC12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="BE12" t="n">
         <v>154327.0</v>
       </c>
       <c r="BF12" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI12" t="s">
         <v>228</v>
       </c>
-      <c r="BG12" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="BL12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BM12"/>
       <c r="BN12" t="n">
         <v>8.556966614E7</v>
       </c>
       <c r="BO12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.5</v>
       </c>
       <c r="BR12" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU12" t="s">
         <v>253</v>
       </c>
-      <c r="BS12" t="s">
+      <c r="BV12" t="s">
         <v>254</v>
-      </c>
-      <c r="BT12" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU12" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV12" t="s">
-        <v>257</v>
       </c>
       <c r="BW12" t="n">
         <v>2015.0</v>
@@ -3273,30 +3300,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA12" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G13" t="n">
         <v>1.160517</v>
@@ -3305,7 +3335,7 @@
         <v>103.740444</v>
       </c>
       <c r="I13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J13" t="n">
         <v>2.7</v>
@@ -3317,24 +3347,24 @@
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R13"/>
       <c r="S13"/>
       <c r="T13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="U13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W13"/>
       <c r="X13" t="n">
@@ -3347,38 +3377,38 @@
         <v>30.0</v>
       </c>
       <c r="AA13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB13"/>
       <c r="AC13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD13" t="n">
         <v>5.0</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG13" t="n">
         <v>0.0</v>
       </c>
       <c r="AH13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI13" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ13"/>
       <c r="AK13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL13" t="n">
         <v>0.0</v>
       </c>
       <c r="AM13"/>
       <c r="AN13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO13" t="n">
         <v>1.0</v>
@@ -3394,81 +3424,81 @@
         <v>208</v>
       </c>
       <c r="AT13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU13" t="n">
         <v>0.0</v>
       </c>
       <c r="AV13"/>
       <c r="AW13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY13"/>
       <c r="AZ13"/>
       <c r="BA13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB13"/>
       <c r="BC13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="BE13" t="n">
         <v>154327.0</v>
       </c>
       <c r="BF13" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI13" t="s">
         <v>228</v>
       </c>
-      <c r="BG13" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI13" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ13" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="BL13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BM13"/>
       <c r="BN13" t="n">
         <v>8.556966614E7</v>
       </c>
       <c r="BO13" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ13" t="n">
         <v>4.5</v>
       </c>
       <c r="BR13" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU13" t="s">
         <v>253</v>
       </c>
-      <c r="BS13" t="s">
+      <c r="BV13" t="s">
         <v>254</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV13" t="s">
-        <v>257</v>
       </c>
       <c r="BW13" t="n">
         <v>2015.0</v>
@@ -3480,30 +3510,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA13" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G14" t="n">
         <v>1.160517</v>
@@ -3512,7 +3545,7 @@
         <v>103.740444</v>
       </c>
       <c r="I14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J14" t="n">
         <v>2.4383999999999997</v>
@@ -3524,24 +3557,24 @@
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R14"/>
       <c r="S14"/>
       <c r="T14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="V14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W14"/>
       <c r="X14" t="n">
@@ -3556,34 +3589,34 @@
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD14" t="n">
         <v>0.0</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG14" t="n">
         <v>0.0</v>
       </c>
       <c r="AH14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI14" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ14"/>
       <c r="AK14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL14" t="n">
         <v>0.0</v>
       </c>
       <c r="AM14"/>
       <c r="AN14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO14" t="n">
         <v>0.0</v>
@@ -3595,85 +3628,85 @@
       </c>
       <c r="AS14"/>
       <c r="AT14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU14" t="n">
         <v>0.0</v>
       </c>
       <c r="AV14"/>
       <c r="AW14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY14" t="s">
         <v>212</v>
       </c>
       <c r="AZ14" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="BA14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB14"/>
       <c r="BC14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="BE14" t="n">
         <v>983578.0</v>
       </c>
       <c r="BF14" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI14" t="s">
         <v>228</v>
       </c>
-      <c r="BG14" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH14" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI14" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ14" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK14" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BL14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BM14"/>
       <c r="BN14" t="n">
         <v>6.0139203620000005E7</v>
       </c>
       <c r="BO14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ14" t="n">
         <v>4.5</v>
       </c>
       <c r="BR14" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU14" t="s">
         <v>253</v>
       </c>
-      <c r="BS14" t="s">
+      <c r="BV14" t="s">
         <v>254</v>
-      </c>
-      <c r="BT14" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU14" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV14" t="s">
-        <v>257</v>
       </c>
       <c r="BW14" t="n">
         <v>2015.0</v>
@@ -3685,30 +3718,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA14" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G15" t="n">
         <v>1.160517</v>
@@ -3717,7 +3753,7 @@
         <v>103.740444</v>
       </c>
       <c r="I15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J15" t="n">
         <v>5.1816</v>
@@ -3729,24 +3765,24 @@
       <c r="M15"/>
       <c r="N15"/>
       <c r="O15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R15"/>
       <c r="S15"/>
       <c r="T15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="V15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W15"/>
       <c r="X15" t="n">
@@ -3759,38 +3795,38 @@
         <v>50.0</v>
       </c>
       <c r="AA15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AB15"/>
       <c r="AC15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD15" t="n">
         <v>1.0</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG15" t="n">
         <v>0.0</v>
       </c>
       <c r="AH15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI15" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ15"/>
       <c r="AK15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL15" t="n">
         <v>20.0</v>
       </c>
       <c r="AM15"/>
       <c r="AN15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="n">
         <v>1.0</v>
@@ -3804,83 +3840,83 @@
       </c>
       <c r="AS15"/>
       <c r="AT15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU15" t="n">
         <v>0.0</v>
       </c>
       <c r="AV15"/>
       <c r="AW15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY15"/>
       <c r="AZ15" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="BA15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB15"/>
       <c r="BC15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="BE15" t="n">
         <v>983578.0</v>
       </c>
       <c r="BF15" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI15" t="s">
         <v>228</v>
       </c>
-      <c r="BG15" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH15" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI15" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BK15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BL15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BM15"/>
       <c r="BN15" t="n">
         <v>6.0139203620000005E7</v>
       </c>
       <c r="BO15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ15" t="n">
         <v>4.5</v>
       </c>
       <c r="BR15" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT15" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU15" t="s">
         <v>253</v>
       </c>
-      <c r="BS15" t="s">
+      <c r="BV15" t="s">
         <v>254</v>
-      </c>
-      <c r="BT15" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU15" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>257</v>
       </c>
       <c r="BW15" t="n">
         <v>2015.0</v>
@@ -3892,30 +3928,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA15" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G16" t="n">
         <v>1.160517</v>
@@ -3924,7 +3963,7 @@
         <v>103.740444</v>
       </c>
       <c r="I16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J16" t="n">
         <v>6.096</v>
@@ -3936,24 +3975,24 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R16"/>
       <c r="S16"/>
       <c r="T16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W16"/>
       <c r="X16" t="n">
@@ -3966,18 +4005,18 @@
         <v>30.0</v>
       </c>
       <c r="AA16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AB16"/>
       <c r="AC16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD16" t="n">
         <v>0.0</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="n">
         <v>0.0</v>
@@ -3986,14 +4025,14 @@
       <c r="AI16"/>
       <c r="AJ16"/>
       <c r="AK16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="n">
         <v>15.0</v>
       </c>
       <c r="AM16"/>
       <c r="AN16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="n">
         <v>1.0</v>
@@ -4005,83 +4044,83 @@
       <c r="AR16"/>
       <c r="AS16"/>
       <c r="AT16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU16" t="n">
         <v>0.0</v>
       </c>
       <c r="AV16"/>
       <c r="AW16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY16" t="s">
         <v>213</v>
       </c>
       <c r="AZ16"/>
       <c r="BA16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB16"/>
       <c r="BC16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="BE16" t="n">
         <v>497657.0</v>
       </c>
       <c r="BF16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI16" t="s">
         <v>228</v>
       </c>
-      <c r="BG16" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="BK16" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="BL16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BM16"/>
       <c r="BN16" t="n">
         <v>8.460194366E7</v>
       </c>
       <c r="BO16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ16" t="n">
         <v>4.5</v>
       </c>
       <c r="BR16" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU16" t="s">
         <v>253</v>
       </c>
-      <c r="BS16" t="s">
+      <c r="BV16" t="s">
         <v>254</v>
-      </c>
-      <c r="BT16" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV16" t="s">
-        <v>257</v>
       </c>
       <c r="BW16" t="n">
         <v>2015.0</v>
@@ -4093,30 +4132,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ16" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA16" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G17" t="n">
         <v>1.160517</v>
@@ -4125,7 +4167,7 @@
         <v>103.740444</v>
       </c>
       <c r="I17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J17" t="n">
         <v>6.5</v>
@@ -4137,24 +4179,24 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R17"/>
       <c r="S17"/>
       <c r="T17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="U17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W17"/>
       <c r="X17" t="n">
@@ -4167,38 +4209,38 @@
         <v>45.0</v>
       </c>
       <c r="AA17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB17"/>
       <c r="AC17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD17" t="n">
         <v>5.0</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="n">
         <v>0.0</v>
       </c>
       <c r="AH17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI17" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ17"/>
       <c r="AK17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="n">
         <v>0.0</v>
       </c>
       <c r="AM17"/>
       <c r="AN17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO17" t="n">
         <v>0.0</v>
@@ -4210,81 +4252,81 @@
       </c>
       <c r="AS17"/>
       <c r="AT17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AU17" t="n">
         <v>5.0</v>
       </c>
       <c r="AV17"/>
       <c r="AW17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY17"/>
       <c r="AZ17"/>
       <c r="BA17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB17"/>
       <c r="BC17" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="BE17" t="n">
         <v>497657.0</v>
       </c>
       <c r="BF17" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI17" t="s">
         <v>228</v>
       </c>
-      <c r="BG17" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="BK17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="BL17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BM17"/>
       <c r="BN17" t="n">
         <v>8.460194366E7</v>
       </c>
       <c r="BO17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ17" t="n">
         <v>4.5</v>
       </c>
       <c r="BR17" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS17" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT17" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU17" t="s">
         <v>253</v>
       </c>
-      <c r="BS17" t="s">
+      <c r="BV17" t="s">
         <v>254</v>
-      </c>
-      <c r="BT17" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU17" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV17" t="s">
-        <v>257</v>
       </c>
       <c r="BW17" t="n">
         <v>2015.0</v>
@@ -4296,30 +4338,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ17" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA17" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G18" t="n">
         <v>1.160517</v>
@@ -4328,7 +4373,7 @@
         <v>103.740444</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J18" t="n">
         <v>6.096</v>
@@ -4340,24 +4385,24 @@
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R18"/>
       <c r="S18"/>
       <c r="T18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="W18"/>
       <c r="X18" t="n">
@@ -4370,18 +4415,18 @@
         <v>7.0</v>
       </c>
       <c r="AA18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB18"/>
       <c r="AC18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD18" t="n">
         <v>15.0</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="n">
         <v>0.0</v>
@@ -4390,14 +4435,14 @@
       <c r="AI18"/>
       <c r="AJ18"/>
       <c r="AK18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL18" t="n">
         <v>15.0</v>
       </c>
       <c r="AM18"/>
       <c r="AN18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO18" t="n">
         <v>3.0</v>
@@ -4416,74 +4461,74 @@
       <c r="AU18"/>
       <c r="AV18"/>
       <c r="AW18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY18"/>
       <c r="AZ18"/>
       <c r="BA18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB18"/>
       <c r="BC18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="BE18" t="n">
         <v>46745.0</v>
       </c>
       <c r="BF18" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI18" t="s">
         <v>228</v>
       </c>
-      <c r="BG18" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH18" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI18" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ18" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="BK18" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="BL18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BM18"/>
       <c r="BN18" t="n">
         <v>8.345387974000001E7</v>
       </c>
       <c r="BO18" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ18" t="n">
         <v>4.5</v>
       </c>
       <c r="BR18" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS18" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT18" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU18" t="s">
         <v>253</v>
       </c>
-      <c r="BS18" t="s">
+      <c r="BV18" t="s">
         <v>254</v>
-      </c>
-      <c r="BT18" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU18" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV18" t="s">
-        <v>257</v>
       </c>
       <c r="BW18" t="n">
         <v>2015.0</v>
@@ -4495,30 +4540,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ18" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA18" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" t="n">
         <v>1.160517</v>
@@ -4527,7 +4575,7 @@
         <v>103.740444</v>
       </c>
       <c r="I19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J19" t="n">
         <v>3.048</v>
@@ -4539,24 +4587,24 @@
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R19"/>
       <c r="S19"/>
       <c r="T19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="W19"/>
       <c r="X19" t="n">
@@ -4569,34 +4617,34 @@
         <v>9.0</v>
       </c>
       <c r="AA19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19"/>
       <c r="AE19"/>
       <c r="AF19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="n">
         <v>0.0</v>
       </c>
       <c r="AH19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI19" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ19"/>
       <c r="AK19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="n">
         <v>80.0</v>
       </c>
       <c r="AM19"/>
       <c r="AN19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO19" t="n">
         <v>1.0</v>
@@ -4612,81 +4660,81 @@
         <v>210</v>
       </c>
       <c r="AT19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU19" t="n">
         <v>0.0</v>
       </c>
       <c r="AV19"/>
       <c r="AW19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY19"/>
       <c r="AZ19"/>
       <c r="BA19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB19"/>
       <c r="BC19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="BE19" t="n">
         <v>46745.0</v>
       </c>
       <c r="BF19" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH19" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI19" t="s">
         <v>228</v>
       </c>
-      <c r="BG19" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="BK19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="BL19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BM19"/>
       <c r="BN19" t="n">
         <v>8.345387974000001E7</v>
       </c>
       <c r="BO19" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP19" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ19" t="n">
         <v>4.5</v>
       </c>
       <c r="BR19" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT19" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU19" t="s">
         <v>253</v>
       </c>
-      <c r="BS19" t="s">
+      <c r="BV19" t="s">
         <v>254</v>
-      </c>
-      <c r="BT19" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU19" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV19" t="s">
-        <v>257</v>
       </c>
       <c r="BW19" t="n">
         <v>2015.0</v>
@@ -4698,30 +4746,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ19" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA19" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G20" t="n">
         <v>1.160517</v>
@@ -4730,7 +4781,7 @@
         <v>103.740444</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
@@ -4742,24 +4793,24 @@
       <c r="M20"/>
       <c r="N20"/>
       <c r="O20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R20"/>
       <c r="S20"/>
       <c r="T20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="W20"/>
       <c r="X20" t="n">
@@ -4772,38 +4823,38 @@
         <v>40.0</v>
       </c>
       <c r="AA20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB20"/>
       <c r="AC20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AD20" t="n">
         <v>5.0</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="n">
         <v>0.0</v>
       </c>
       <c r="AH20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI20" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ20"/>
       <c r="AK20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL20" t="n">
         <v>0.0</v>
       </c>
       <c r="AM20"/>
       <c r="AN20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO20" t="n">
         <v>0.0</v>
@@ -4815,81 +4866,81 @@
       </c>
       <c r="AS20"/>
       <c r="AT20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU20" t="n">
         <v>0.0</v>
       </c>
       <c r="AV20"/>
       <c r="AW20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY20"/>
       <c r="AZ20"/>
       <c r="BA20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB20"/>
       <c r="BC20" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="BE20" t="n">
         <v>55974.0</v>
       </c>
       <c r="BF20" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI20" t="s">
         <v>228</v>
       </c>
-      <c r="BG20" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ20" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="BK20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BL20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BM20"/>
       <c r="BN20" t="n">
         <v>1.101362699E8</v>
       </c>
       <c r="BO20" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP20" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ20" t="n">
         <v>4.5</v>
       </c>
       <c r="BR20" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT20" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU20" t="s">
         <v>253</v>
       </c>
-      <c r="BS20" t="s">
+      <c r="BV20" t="s">
         <v>254</v>
-      </c>
-      <c r="BT20" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU20" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV20" t="s">
-        <v>257</v>
       </c>
       <c r="BW20" t="n">
         <v>2015.0</v>
@@ -4901,30 +4952,33 @@
         <v>23.0</v>
       </c>
       <c r="BZ20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA20" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G21" t="n">
         <v>1.160517</v>
@@ -4933,7 +4987,7 @@
         <v>103.740444</v>
       </c>
       <c r="I21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J21" t="n">
         <v>2.7</v>
@@ -4945,24 +4999,24 @@
       <c r="M21"/>
       <c r="N21"/>
       <c r="O21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R21"/>
       <c r="S21"/>
       <c r="T21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="W21"/>
       <c r="X21" t="n">
@@ -4975,38 +5029,38 @@
         <v>35.0</v>
       </c>
       <c r="AA21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB21"/>
       <c r="AC21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD21" t="n">
         <v>0.0</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="n">
         <v>0.0</v>
       </c>
       <c r="AH21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI21" t="n">
         <v>0.0</v>
       </c>
       <c r="AJ21"/>
       <c r="AK21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL21" t="n">
         <v>0.0</v>
       </c>
       <c r="AM21"/>
       <c r="AN21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO21" t="n">
         <v>0.0</v>
@@ -5018,81 +5072,81 @@
       </c>
       <c r="AS21"/>
       <c r="AT21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU21" t="n">
         <v>0.0</v>
       </c>
       <c r="AV21"/>
       <c r="AW21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AX21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AY21"/>
       <c r="AZ21"/>
       <c r="BA21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BB21"/>
       <c r="BC21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BD21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="BE21" t="n">
         <v>55974.0</v>
       </c>
       <c r="BF21" t="s">
+        <v>225</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>226</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI21" t="s">
         <v>228</v>
       </c>
-      <c r="BG21" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH21" t="s">
-        <v>230</v>
-      </c>
-      <c r="BI21" t="s">
-        <v>231</v>
-      </c>
       <c r="BJ21" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="BK21" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BL21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BM21"/>
       <c r="BN21" t="n">
         <v>1.101362699E8</v>
       </c>
       <c r="BO21" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BP21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="BQ21" t="n">
         <v>4.5</v>
       </c>
       <c r="BR21" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT21" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU21" t="s">
         <v>253</v>
       </c>
-      <c r="BS21" t="s">
+      <c r="BV21" t="s">
         <v>254</v>
-      </c>
-      <c r="BT21" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU21" t="s">
-        <v>256</v>
-      </c>
-      <c r="BV21" t="s">
-        <v>257</v>
       </c>
       <c r="BW21" t="n">
         <v>2015.0</v>
@@ -5104,10 +5158,13 @@
         <v>23.0</v>
       </c>
       <c r="BZ21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="CA21" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
